--- a/docs/就職活動メモシステム.機能一覧.xlsx
+++ b/docs/就職活動メモシステム.機能一覧.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>使用システムごとに、項目1～項目50の表示名・表示するかどうか・必須かどうか・型（文字列型／数値型／メモ型／チェックボックス）・表示桁数・URLかどうか・項目表示順・コードID・初期値・検索項目（検索方式）を変更する。コードIDを指定すると、その項目は編集時にコードマスタのドロップダウンリストになる。チェックボックスを指定した項目は一覧・編集画面でチェックボックスとして扱う。初期値に %Y・%m・%d・%H・%i・%s を含めると、新規登録時にシステム日時へ置換される。検索項目で検索方式を指定した項目は、メモ一覧の検索部で検索できる</t>
+          <t>使用システムごとに、項目1～項目50の表示名・表示するかどうか・必須かどうか・型（文字列型／数値型／メモ型／チェックボックス／日付型）・表示桁数・URLかどうか・項目表示順・コードID・初期値・検索項目（検索方式）を変更する。コードIDを指定すると、その項目は編集時にコードマスタのドロップダウンリストになる。チェックボックスを指定した項目は一覧・編集画面でチェックボックスとして扱う。日付型を指定した項目は編集画面でカレンダー入力となり、値は数字のみ（yyyyMMdd）で保存され、一覧・編集画面では yyyy/mm/dd で表示する。初期値に %Y・%m・%d・%H・%i・%s を含めると、新規登録時にシステム日時へ置換される。検索項目で検索方式を指定した項目は、メモ一覧の検索部で検索できる</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
